--- a/pidsg25-06.xlsx
+++ b/pidsg25-06.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/forecast25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D861AC-504B-E84C-BBB4-BBAA39C52A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F514CF8-EB8E-4B4D-966B-6814FF480D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3340" yWindow="500" windowWidth="21100" windowHeight="11860" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6560" yWindow="6520" windowWidth="21080" windowHeight="11860" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="from_alvin" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="59">
   <si>
     <t>FY24</t>
   </si>
@@ -188,16 +188,47 @@
   <si>
     <t>Demand-PIDSG</t>
   </si>
+  <si>
+    <t>Total cost-Man</t>
+  </si>
+  <si>
+    <t>Procurement</t>
+  </si>
+  <si>
+    <t>Total cost- AI</t>
+  </si>
+  <si>
+    <t>Cumulative Man</t>
+  </si>
+  <si>
+    <t>Cumulative AI</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unhedged cost </t>
+  </si>
+  <si>
+    <t>trans mg</t>
+  </si>
+  <si>
+    <t>Storage</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="mm/yy"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -270,7 +301,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -286,8 +317,14 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -931,15 +968,16 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Eval!$L$4</c:f>
+              <c:f>Eval!$L$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -949,32 +987,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Eval!$K$5:$K$16</c:f>
+              <c:f>Eval!$K$9:$K$20</c:f>
               <c:numCache>
                 <c:formatCode>mm/dd/yy</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1019,7 +1043,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Eval!$L$5:$L$16</c:f>
+              <c:f>Eval!$L$9:$L$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1062,7 +1086,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-8DB7-401F-BF5C-D06FE4F1A5C3}"/>
@@ -1074,7 +1097,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Eval!$M$4</c:f>
+              <c:f>Eval!$M$8</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1084,32 +1107,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
+          <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>Eval!$K$5:$K$16</c:f>
+              <c:f>Eval!$K$9:$K$20</c:f>
               <c:numCache>
                 <c:formatCode>mm/dd/yy</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1154,7 +1163,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Eval!$M$5:$M$16</c:f>
+              <c:f>Eval!$M$9:$M$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
@@ -1197,7 +1206,6 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-8DB7-401F-BF5C-D06FE4F1A5C3}"/>
@@ -1212,11 +1220,10 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
+        <c:gapWidth val="150"/>
         <c:axId val="1156906560"/>
         <c:axId val="1156920480"/>
-      </c:lineChart>
+      </c:barChart>
       <c:dateAx>
         <c:axId val="1156906560"/>
         <c:scaling>
@@ -1461,7 +1468,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Eval!$G$59</c:f>
+              <c:f>Eval!$G$63</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1496,7 +1503,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Eval!$F$60:$F$69</c:f>
+              <c:f>Eval!$F$64:$F$73</c:f>
               <c:numCache>
                 <c:formatCode>mm/dd/yy</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1535,7 +1542,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Eval!$G$60:$G$69</c:f>
+              <c:f>Eval!$G$64:$G$73</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00</c:formatCode>
                 <c:ptCount val="10"/>
@@ -1750,6 +1757,1644 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Storage Cost (KUSD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Eval!$J$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Storage cost</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Eval!$J$42:$J$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>2641.4609053497929</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>11150.334362139914</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13631.044238683122</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18080.954218106992</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22103.26646090531</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>24514.529012345633</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21460.259465020532</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17123.035956790081</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11459.616460905305</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10377.601286008185</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6683.3818930040688</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3632.1666152262928</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-702C-C347-A492-F695AAD7963D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1339677743"/>
+        <c:axId val="1339644543"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1339677743"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1339644543"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1339644543"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1339677743"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Cumutaive Cost</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Eval!$S$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cumulative Man</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Eval!$R$42:$R$53</c:f>
+              <c:numCache>
+                <c:formatCode>mm/dd/yy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>45772</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45802</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45833</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45863</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45894</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45925</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45955</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46016</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46047</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46106</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Eval!$S$42:$S$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>446884</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>687149</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1161939.5789473685</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1512998.7368421054</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1864057.8947368423</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2124510.6710526319</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2403467.1361689111</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2737231.1586606628</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3208585.1538277245</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3364393.2063859291</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3644271.4050940475</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3879440.5531492545</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-04BE-184D-B080-BA0BA9DA7554}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Eval!$T$41</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cumulative AI</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Eval!$R$42:$R$53</c:f>
+              <c:numCache>
+                <c:formatCode>mm/dd/yy</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>45772</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45802</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45833</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45863</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45894</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45925</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45955</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46016</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46047</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46106</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Eval!$T$42:$T$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>542281.50637903402</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>793696.84074117395</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1372327.4382430147</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1849345.7613032269</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2320020.2366062365</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2624472.9133926621</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2794021.1728576827</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2959232.2088144729</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3118779.8252753783</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3277245.4265613863</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3432016.8084543906</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3583736.9750696169</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-04BE-184D-B080-BA0BA9DA7554}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1035213215"/>
+        <c:axId val="1035064015"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1035213215"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="mm/dd/yy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1035064015"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1035064015"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1035213215"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Eval!$H$63</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Demand-PIDSG</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Eval!$F$64:$F$73</c:f>
+              <c:numCache>
+                <c:formatCode>mm/dd/yy</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>45833</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45863</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45894</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45925</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45955</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46016</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46047</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46106</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Eval!$H$64:$H$73</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>9902.2633744855975</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8326.9032921810704</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8326.9032921810704</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6237.1399176954737</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5208.333333333333</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6237.1399176954737</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7298.0967078189306</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3632.9732510288068</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5722.7366255144034</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5208.333333333333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4A6D-124B-ABC7-86DA19CBACF7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1272780047"/>
+        <c:axId val="1272781759"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1272780047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="mm/dd/yy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1272781759"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1272781759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1272780047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB"/>
+              <a:t>Silver</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-GB" baseline="0"/>
+              <a:t>/unit</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-GB"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-GB"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>Eval!$F$76:$F$85</c:f>
+              <c:numCache>
+                <c:formatCode>mm/dd/yy</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>45833</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45863</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45894</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45925</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45955</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45986</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46016</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46047</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46078</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>46106</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Eval!$G$76:$G$85</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>53.426836124934098</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>39.311872739758563</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39.953569891639354</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30.435688143403549</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.839472792068729</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31.481467980150882</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>47.069311240367171</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23.483989987257964</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>42.915160296320984</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>39.263726598818941</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3038-7F4A-BFA2-1618266ED775}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1671489391"/>
+        <c:axId val="1279847071"/>
+      </c:barChart>
+      <c:dateAx>
+        <c:axId val="1671489391"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="mm/dd/yy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1279847071"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1279847071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1671489391"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1870,6 +3515,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -3379,20 +5184,2032 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>102870</xdr:rowOff>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>232410</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:colOff>207010</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3432,7 +7249,7 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>388620</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>72390</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3462,13 +7279,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>387350</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>58</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>844550</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -3489,6 +7306,150 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>939800</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B9BED4D-12BA-2595-FC91-323B7D27C0AF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{608DF2F7-8347-959E-38E7-6DB658FBE53D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>787400</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90588233-48E1-9C4B-045A-707290AD7502}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>927100</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B04E3114-A8F1-7CCF-00DB-196F50F309E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3681,10 +7642,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="11"/>
+      <c r="C3" s="12"/>
       <c r="D3" s="1">
         <v>45383</v>
       </c>
@@ -4146,10 +8107,10 @@
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="11"/>
+      <c r="C14" s="12"/>
       <c r="D14" s="1">
         <v>45748</v>
       </c>
@@ -4628,7 +8589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.83203125" customWidth="1"/>
@@ -5055,6 +9016,244 @@
       </c>
       <c r="O9">
         <v>2905085</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="D11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="E11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="F11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="H11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="I11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="J11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="K11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="L11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="M11">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="N11">
+        <v>31.103999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C12">
+        <f>C4/C11</f>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f t="shared" ref="D12:N12" si="0">D4/D11</f>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>2282.6646090534982</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>3729.4238683127573</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>3311.471193415638</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>2925.6687242798353</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="0"/>
+        <v>3729.4238683127573</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C13">
+        <f>C6/C11</f>
+        <v>13888.888888888889</v>
+      </c>
+      <c r="D13">
+        <f t="shared" ref="D13:N13" si="1">D6/D11</f>
+        <v>12037.037037037036</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>15740.740740740741</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>22222.222222222223</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>14039.126800411523</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>8761.3811728395067</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="1"/>
+        <v>12528.870884773663</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="1"/>
+        <v>6960.9375</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>13391.010802469136</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>5555.5555555555557</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="1"/>
+        <v>23148.14814814815</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="1"/>
+        <v>10185.185185185186</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <f>SUM(C12:C13)</f>
+        <v>13888.888888888889</v>
+      </c>
+      <c r="D15">
+        <f t="shared" ref="D15:N15" si="2">SUM(D12:D13)</f>
+        <v>12037.037037037036</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>15740.740740740741</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="2"/>
+        <v>22222.222222222223</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>16321.79140946502</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>12490.805041152264</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>15840.342078189302</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="2"/>
+        <v>9886.6062242798362</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="2"/>
+        <v>17120.434670781895</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="2"/>
+        <v>5555.5555555555557</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="2"/>
+        <v>23148.14814814815</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="2"/>
+        <v>10185.185185185186</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <f>C9*C11/C6</f>
+        <v>15.399575999999998</v>
+      </c>
+      <c r="D17">
+        <f>D9*D11/D6</f>
+        <v>16.865612307692306</v>
+      </c>
+      <c r="E17">
+        <f t="shared" ref="E17:N17" si="3">E9*E11/E6</f>
+        <v>18.138790588235292</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>18.871335000000002</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="3"/>
+        <v>18.23888363145878</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="3"/>
+        <v>18.308186441797485</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="3"/>
+        <v>18.978565761179169</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>19.454563411896746</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="3"/>
+        <v>19.538480243161093</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="3"/>
+        <v>19.223279999999999</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="3"/>
+        <v>18.689356799999999</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="3"/>
+        <v>18.908149090909092</v>
       </c>
     </row>
   </sheetData>
@@ -5069,7 +9268,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.83203125" customWidth="1"/>
@@ -5643,6 +9842,239 @@
       <c r="N13">
         <f t="shared" si="1"/>
         <v>1.1469515312049816</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="D15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="E15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="F15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="G15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="H15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="I15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="J15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="K15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="L15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="M15">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="N15">
+        <v>31.103999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <f>C13*C15</f>
+        <v>43.894292210526316</v>
+      </c>
+      <c r="D16">
+        <v>43.894292210526316</v>
+      </c>
+      <c r="E16">
+        <f t="shared" ref="E16:N16" si="2">E13*E15</f>
+        <v>45.455221894736837</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="2"/>
+        <v>30.303481263157895</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>30.303481263157895</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>10.101228631578946</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>53.559641302325581</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="2"/>
+        <v>53.512351317440405</v>
+      </c>
+      <c r="K16">
+        <v>53.512351317440405</v>
+      </c>
+      <c r="L16">
+        <v>53.512351317440405</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="2"/>
+        <v>44.593385194479296</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="2"/>
+        <v>35.674780426599746</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <f>C8*C15/C3</f>
+        <v>19.305415384615383</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ref="D17:N17" si="3">D8*D15/D3</f>
+        <v>19.960476923076921</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="3"/>
+        <v>19.991852999999999</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="3"/>
+        <v>19.991852999999999</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="3"/>
+        <v>19.991852999999999</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="3"/>
+        <v>19.991852999999999</v>
+      </c>
+      <c r="I17">
+        <f>I8*I15/I3</f>
+        <v>19.991879999999998</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>19.991879999999998</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="3"/>
+        <v>19.991879999999998</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="3"/>
+        <v>19.991879999999998</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="3"/>
+        <v>19.991879999999998</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="3"/>
+        <v>19.991879999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C19">
+        <v>43.894292210526316</v>
+      </c>
+      <c r="D19">
+        <v>43.894292210526316</v>
+      </c>
+      <c r="E19">
+        <v>45.455221894736837</v>
+      </c>
+      <c r="F19">
+        <v>30.303481263157895</v>
+      </c>
+      <c r="G19">
+        <v>30.303481263157895</v>
+      </c>
+      <c r="H19">
+        <v>10.101228631578946</v>
+      </c>
+      <c r="I19">
+        <v>53.559641302325581</v>
+      </c>
+      <c r="J19">
+        <v>53.512351317440405</v>
+      </c>
+      <c r="K19">
+        <v>53.512351317440405</v>
+      </c>
+      <c r="L19">
+        <v>53.512351317440405</v>
+      </c>
+      <c r="M19">
+        <v>44.593385194479296</v>
+      </c>
+      <c r="N19">
+        <v>35.674780426599746</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C21">
+        <v>43.894292210526316</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C22">
+        <v>43.894292210526316</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C23">
+        <v>45.455221894736837</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C24">
+        <v>30.303481263157895</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C25">
+        <v>30.303481263157895</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C26">
+        <v>30.303481263157895</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C27">
+        <v>53.559641302325581</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C28">
+        <v>53.512351317440405</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C29">
+        <v>53.512351317440405</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C30">
+        <v>53.512351317440405</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C31">
+        <v>44.593385194479296</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C32">
+        <v>35.674780426599746</v>
       </c>
     </row>
   </sheetData>
@@ -6163,480 +10595,367 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C0A8C1-78FE-4A69-B39B-104D697149B8}">
-  <dimension ref="B3:M69"/>
+  <dimension ref="B1:T85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
     <col min="7" max="7" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="H2" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2">
+        <v>1316511.5530000001</v>
+      </c>
+      <c r="J2">
+        <v>765195</v>
+      </c>
+    </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+      <c r="H3" s="13"/>
+      <c r="I3">
+        <v>2116045</v>
+      </c>
+      <c r="J3">
+        <v>2116045</v>
+      </c>
+      <c r="K3">
+        <v>160216</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <f>SUM(I2:I3)</f>
+        <v>3432556.5530000003</v>
+      </c>
+      <c r="J4">
+        <f>SUM(J2:J3)</f>
+        <v>2881240</v>
+      </c>
+      <c r="K4">
+        <f>SUM(K3,J4)</f>
+        <v>3041456</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <v>3432556.5529999998</v>
+      </c>
+      <c r="J5">
+        <v>2881240</v>
+      </c>
+      <c r="K5">
+        <v>3041456</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F7" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="C4" s="8" t="s">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M8" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="7">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B9" s="7">
         <v>45772</v>
       </c>
-      <c r="C5">
+      <c r="C9">
         <v>1.5288157894736842</v>
       </c>
-      <c r="D5">
+      <c r="D9">
         <v>1.4112105263157895</v>
       </c>
-      <c r="E5">
+      <c r="E9">
         <v>31.103999999999999</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F9" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G9" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="H5">
-        <f>C5*E5*F5</f>
+      <c r="H9">
+        <f>C9*E9*F9</f>
         <v>232380</v>
       </c>
-      <c r="I5">
-        <f>D5*E5*G5</f>
+      <c r="I9">
+        <f>D9*E9*G9</f>
         <v>214504</v>
       </c>
-      <c r="J5">
-        <f>H5+I5</f>
+      <c r="J9">
+        <f>H9+I9</f>
         <v>446884</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K9" s="7">
         <v>45772</v>
       </c>
-      <c r="L5">
-        <f>I5</f>
+      <c r="L9">
+        <f>I9</f>
         <v>214504</v>
       </c>
-      <c r="M5">
-        <f>L21</f>
+      <c r="M9">
+        <f>L25</f>
         <v>307260.04547368421</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" s="7">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B10" s="7">
         <v>45802</v>
       </c>
-      <c r="C6">
+      <c r="C10">
         <v>1.5806907894736841</v>
       </c>
-      <c r="D6">
+      <c r="D10">
         <v>0</v>
       </c>
-      <c r="E6">
+      <c r="E10">
         <v>31.103999999999999</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F10" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G10" s="8">
         <v>192.90123456790116</v>
       </c>
-      <c r="H6">
-        <f t="shared" ref="H6:H16" si="0">C6*E6*F6</f>
+      <c r="H10">
+        <f t="shared" ref="H10:H20" si="0">C10*E10*F10</f>
         <v>240264.99999999997</v>
       </c>
-      <c r="I6">
-        <f t="shared" ref="I6:I16" si="1">D6*E6*G6</f>
+      <c r="I10">
+        <f t="shared" ref="I10:I20" si="1">D10*E10*G10</f>
         <v>0</v>
       </c>
-      <c r="J6">
-        <f t="shared" ref="J6:J16" si="2">H6+I6</f>
+      <c r="J10">
+        <f t="shared" ref="J10:J20" si="2">H10+I10</f>
         <v>240264.99999999997</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K10" s="7">
         <v>45802</v>
       </c>
-      <c r="L6">
-        <f>L5+I6</f>
+      <c r="L10">
+        <f>L9+I10</f>
         <v>214504</v>
       </c>
-      <c r="M6">
-        <f t="shared" ref="M6:M16" si="3">L22</f>
+      <c r="M10">
+        <f t="shared" ref="M10:M20" si="3">L26</f>
         <v>307260.04547368421</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B7" s="7">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="7">
         <v>45833</v>
       </c>
-      <c r="C7">
+      <c r="C11">
         <v>1.6237697368421053</v>
       </c>
-      <c r="D7">
+      <c r="D11">
         <v>1.4613947368421052</v>
       </c>
-      <c r="E7">
+      <c r="E11">
         <v>31.103999999999999</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F11" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G11" s="8">
         <v>5015.4320987654328</v>
       </c>
-      <c r="H7">
+      <c r="H11">
         <f t="shared" si="0"/>
         <v>246813</v>
       </c>
-      <c r="I7">
+      <c r="I11">
         <f t="shared" si="1"/>
         <v>227977.57894736843</v>
       </c>
-      <c r="J7">
+      <c r="J11">
         <f t="shared" si="2"/>
         <v>474790.57894736843</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K11" s="7">
         <v>45833</v>
       </c>
-      <c r="L7">
-        <f t="shared" ref="L7:L16" si="4">L6+I7</f>
+      <c r="L11">
+        <f t="shared" ref="L11:L20" si="4">L10+I11</f>
         <v>442481.57894736843</v>
       </c>
-      <c r="M7">
+      <c r="M11">
         <f t="shared" si="3"/>
         <v>625446.59873684205</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B8" s="7">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B12" s="7">
         <v>45863</v>
       </c>
-      <c r="C8">
+      <c r="C12">
         <v>1.6237697368421053</v>
       </c>
-      <c r="D8">
+      <c r="D12">
         <v>0.97426315789473683</v>
       </c>
-      <c r="E8">
+      <c r="E12">
         <v>31.103999999999999</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F12" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G12" s="8">
         <v>3440.0720164609056</v>
       </c>
-      <c r="H8">
+      <c r="H12">
         <f t="shared" si="0"/>
         <v>246813</v>
       </c>
-      <c r="I8">
+      <c r="I12">
         <f t="shared" si="1"/>
         <v>104246.15789473685</v>
       </c>
-      <c r="J8">
+      <c r="J12">
         <f t="shared" si="2"/>
         <v>351059.15789473685</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K12" s="7">
         <v>45863</v>
       </c>
-      <c r="L8">
+      <c r="L12">
         <f t="shared" si="4"/>
         <v>546727.73684210528</v>
       </c>
-      <c r="M8">
+      <c r="M12">
         <f t="shared" si="3"/>
         <v>837570.96757894731</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B9" s="7">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B13" s="7">
         <v>45894</v>
       </c>
-      <c r="C9">
+      <c r="C13">
         <v>1.6237697368421053</v>
       </c>
-      <c r="D9">
+      <c r="D13">
         <v>0.97426315789473683</v>
       </c>
-      <c r="E9">
+      <c r="E13">
         <v>31.103999999999999</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F13" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G13" s="8">
         <v>3440.0720164609056</v>
       </c>
-      <c r="H9">
+      <c r="H13">
         <f t="shared" si="0"/>
         <v>246813</v>
       </c>
-      <c r="I9">
+      <c r="I13">
         <f t="shared" si="1"/>
         <v>104246.15789473685</v>
       </c>
-      <c r="J9">
+      <c r="J13">
         <f t="shared" si="2"/>
         <v>351059.15789473685</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K13" s="7">
         <v>45894</v>
       </c>
-      <c r="L9">
+      <c r="L13">
         <f t="shared" si="4"/>
         <v>650973.89473684214</v>
       </c>
-      <c r="M9">
+      <c r="M13">
         <f t="shared" si="3"/>
         <v>1039329.1764210517</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B10" s="7">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B14" s="7">
         <v>45925</v>
       </c>
-      <c r="C10">
+      <c r="C14">
         <v>1.6237697368421053</v>
       </c>
-      <c r="D10">
+      <c r="D14">
         <v>0.32475657894736842</v>
       </c>
-      <c r="E10">
+      <c r="E14">
         <v>31.103999999999999</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F14" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G14" s="8">
         <v>1350.308641975309</v>
       </c>
-      <c r="H10">
+      <c r="H14">
         <f t="shared" si="0"/>
         <v>246813</v>
       </c>
-      <c r="I10">
+      <c r="I14">
         <f t="shared" si="1"/>
         <v>13639.776315789475</v>
       </c>
-      <c r="J10">
+      <c r="J14">
         <f t="shared" si="2"/>
         <v>260452.77631578947</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K14" s="7">
         <v>45925</v>
       </c>
-      <c r="L10">
+      <c r="L14">
         <f t="shared" si="4"/>
         <v>664613.67105263157</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="3"/>
-        <v>1072454.3241951317</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B11" s="7">
-        <v>45955</v>
-      </c>
-      <c r="C11">
-        <v>1.7219534883720931</v>
-      </c>
-      <c r="D11">
-        <v>1.7219534883720931</v>
-      </c>
-      <c r="E11">
-        <v>31.103999999999999</v>
-      </c>
-      <c r="F11" s="8">
-        <v>2764.9176954732511</v>
-      </c>
-      <c r="G11" s="8">
-        <v>2443.4156378600819</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>148088</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="1"/>
-        <v>130868.46511627905</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="2"/>
-        <v>278956.46511627908</v>
-      </c>
-      <c r="K11" s="7">
-        <v>45955</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="4"/>
-        <v>795482.13616891066</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="3"/>
-        <v>1072454.3241951317</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B12" s="7">
-        <v>45986</v>
-      </c>
-      <c r="C12">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="D12">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="E12">
-        <v>31.103999999999999</v>
-      </c>
-      <c r="F12" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="G12" s="8">
-        <v>3469.7788065843624</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
-        <v>148088.00000000003</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>185676.0224917515</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="2"/>
-        <v>333764.02249175153</v>
-      </c>
-      <c r="K12" s="7">
-        <v>45986</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="4"/>
-        <v>981158.15866066213</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="3"/>
-        <v>1072454.3241951317</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B13" s="7">
-        <v>46016</v>
-      </c>
-      <c r="C13">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="D13">
-        <v>2.2939030624099632</v>
-      </c>
-      <c r="E13">
-        <v>31.103999999999999</v>
-      </c>
-      <c r="F13" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="G13" s="8">
-        <v>4530.7355967078192</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="0"/>
-        <v>148088.00000000003</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="1"/>
-        <v>323265.99516706169</v>
-      </c>
-      <c r="J13">
-        <f t="shared" si="2"/>
-        <v>471353.99516706169</v>
-      </c>
-      <c r="K13" s="7">
-        <v>46016</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="4"/>
-        <v>1304424.1538277238</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="3"/>
-        <v>1072454.3241951317</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B14" s="7">
-        <v>46047</v>
-      </c>
-      <c r="C14">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="D14">
-        <v>0.28673497839118917</v>
-      </c>
-      <c r="E14">
-        <v>31.103999999999999</v>
-      </c>
-      <c r="F14" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="G14" s="8">
-        <v>865.61213991769546</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>148088.00000000003</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="1"/>
-        <v>7720.0525582043765</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="2"/>
-        <v>155808.05255820439</v>
-      </c>
-      <c r="K14" s="7">
-        <v>46047</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="4"/>
-        <v>1312144.2063859282</v>
       </c>
       <c r="M14">
         <f t="shared" si="3"/>
@@ -6645,41 +10964,41 @@
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B15" s="7">
-        <v>46078</v>
+        <v>45955</v>
       </c>
       <c r="C15">
-        <v>1.720433105627585</v>
+        <v>1.7219534883720931</v>
       </c>
       <c r="D15">
-        <v>1.4336865095961708</v>
+        <v>1.7219534883720931</v>
       </c>
       <c r="E15">
         <v>31.103999999999999</v>
       </c>
       <c r="F15" s="8">
-        <v>2767.3611111111113</v>
+        <v>2764.9176954732511</v>
       </c>
       <c r="G15" s="8">
-        <v>2955.3755144032921</v>
+        <v>2443.4156378600819</v>
       </c>
       <c r="H15">
         <f t="shared" si="0"/>
-        <v>148088.00000000003</v>
+        <v>148088</v>
       </c>
       <c r="I15">
         <f t="shared" si="1"/>
-        <v>131790.19870811841</v>
+        <v>130868.46511627905</v>
       </c>
       <c r="J15">
         <f t="shared" si="2"/>
-        <v>279878.19870811841</v>
+        <v>278956.46511627908</v>
       </c>
       <c r="K15" s="7">
-        <v>46078</v>
+        <v>45955</v>
       </c>
       <c r="L15">
         <f t="shared" si="4"/>
-        <v>1443934.4050940466</v>
+        <v>795482.13616891066</v>
       </c>
       <c r="M15">
         <f t="shared" si="3"/>
@@ -6688,13 +11007,13 @@
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B16" s="7">
-        <v>46106</v>
+        <v>45986</v>
       </c>
       <c r="C16">
         <v>1.720433105627585</v>
       </c>
       <c r="D16">
-        <v>1.1469515312049816</v>
+        <v>1.720433105627585</v>
       </c>
       <c r="E16">
         <v>31.103999999999999</v>
@@ -6703,7 +11022,7 @@
         <v>2767.3611111111113</v>
       </c>
       <c r="G16" s="8">
-        <v>2440.9722222222217</v>
+        <v>3469.7788065843624</v>
       </c>
       <c r="H16">
         <f t="shared" si="0"/>
@@ -6711,470 +11030,502 @@
       </c>
       <c r="I16">
         <f t="shared" si="1"/>
-        <v>87081.148055206999</v>
+        <v>185676.0224917515</v>
       </c>
       <c r="J16">
         <f t="shared" si="2"/>
-        <v>235169.14805520704</v>
+        <v>333764.02249175153</v>
       </c>
       <c r="K16" s="7">
-        <v>46106</v>
+        <v>45986</v>
       </c>
       <c r="L16">
         <f t="shared" si="4"/>
-        <v>1531015.5531492536</v>
+        <v>981158.15866066213</v>
       </c>
       <c r="M16">
         <f t="shared" si="3"/>
         <v>1072454.3241951317</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="F17">
-        <f>SUM(F5:F16)</f>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B17" s="7">
+        <v>46016</v>
+      </c>
+      <c r="C17">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="D17">
+        <v>2.2939030624099632</v>
+      </c>
+      <c r="E17">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="F17" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="G17" s="8">
+        <v>4530.7355967078192</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="1"/>
+        <v>323265.99516706169</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="2"/>
+        <v>471353.99516706169</v>
+      </c>
+      <c r="K17" s="7">
+        <v>46016</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="4"/>
+        <v>1304424.1538277238</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="3"/>
+        <v>1072454.3241951317</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B18" s="7">
+        <v>46047</v>
+      </c>
+      <c r="C18">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="D18">
+        <v>0.28673497839118917</v>
+      </c>
+      <c r="E18">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="F18" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="G18" s="8">
+        <v>865.61213991769546</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="1"/>
+        <v>7720.0525582043765</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="2"/>
+        <v>155808.05255820439</v>
+      </c>
+      <c r="K18" s="7">
+        <v>46047</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="4"/>
+        <v>1312144.2063859282</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="3"/>
+        <v>1072454.3241951317</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B19" s="7">
+        <v>46078</v>
+      </c>
+      <c r="C19">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="D19">
+        <v>1.4336865095961708</v>
+      </c>
+      <c r="E19">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="F19" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="G19" s="8">
+        <v>2955.3755144032921</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="1"/>
+        <v>131790.19870811841</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="2"/>
+        <v>279878.19870811841</v>
+      </c>
+      <c r="K19" s="7">
+        <v>46078</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="4"/>
+        <v>1443934.4050940466</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="3"/>
+        <v>1072454.3241951317</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B20" s="7">
+        <v>46106</v>
+      </c>
+      <c r="C20">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="D20">
+        <v>1.1469515312049816</v>
+      </c>
+      <c r="E20">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="F20" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="G20" s="8">
+        <v>2440.9722222222217</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="1"/>
+        <v>87081.148055206999</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="2"/>
+        <v>235169.14805520704</v>
+      </c>
+      <c r="K20" s="7">
+        <v>46106</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="4"/>
+        <v>1531015.5531492536</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="3"/>
+        <v>1072454.3241951317</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="F21">
+        <f>SUM(F9:F20)</f>
         <v>45922.710905349784</v>
       </c>
-      <c r="G17" s="8">
-        <f>SUM(G5:G16)</f>
+      <c r="G21" s="8">
+        <f>SUM(G9:G20)</f>
         <v>35031.507201646091</v>
       </c>
-      <c r="I17" s="9">
-        <f>SUM(I5:I16)</f>
+      <c r="H21" s="9">
+        <f>SUM(H9:H20)</f>
+        <v>2348425</v>
+      </c>
+      <c r="I21" s="9">
+        <f>SUM(I9:I20)</f>
         <v>1531015.5531492536</v>
       </c>
-      <c r="J17" s="9">
-        <f>SUM(J5:J16)</f>
+      <c r="J21" s="9">
+        <f>SUM(J9:J20)</f>
         <v>3879440.5531492545</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="I18">
-        <f>I17/G17</f>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="I22">
+        <f>I21/G21</f>
         <v>43.703958962899343</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B19" t="s">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
         <v>26</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F23" t="s">
         <v>36</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="L23" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C20" s="8" t="s">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="C24" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E24" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G24" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H24" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I24" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L20" s="8" t="s">
+      <c r="L24" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B21" s="7">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B25" s="7">
         <v>45772</v>
       </c>
-      <c r="C21">
+      <c r="C25">
         <v>1.5288157894736842</v>
       </c>
-      <c r="D21">
+      <c r="D25">
         <v>1.4112105263157895</v>
       </c>
-      <c r="E21">
+      <c r="E25">
         <v>31.103999999999999</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F25" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G21">
+      <c r="G25">
         <v>7000</v>
       </c>
-      <c r="H21">
-        <f>C21*E21*F21</f>
+      <c r="H25">
+        <f>C25*E25*F25</f>
         <v>232380</v>
       </c>
-      <c r="I21">
-        <f>D21*E21*G21</f>
+      <c r="I25">
+        <f>D25*E25*G25</f>
         <v>307260.04547368421</v>
       </c>
-      <c r="J21">
-        <f>H21+I21</f>
+      <c r="J25">
+        <f>H25+I25</f>
         <v>539640.04547368421</v>
       </c>
-      <c r="L21">
-        <f>I21</f>
+      <c r="L25">
+        <f>I25</f>
         <v>307260.04547368421</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B22" s="7">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B26" s="7">
         <v>45802</v>
       </c>
-      <c r="C22">
+      <c r="C26">
         <v>1.5806907894736841</v>
       </c>
-      <c r="D22">
+      <c r="D26">
         <v>0</v>
       </c>
-      <c r="E22">
+      <c r="E26">
         <v>31.103999999999999</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F26" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G22">
+      <c r="G26">
         <v>7000</v>
       </c>
-      <c r="H22">
-        <f t="shared" ref="H22:H32" si="5">C22*E22*F22</f>
+      <c r="H26">
+        <f t="shared" ref="H26:H36" si="5">C26*E26*F26</f>
         <v>240264.99999999997</v>
       </c>
-      <c r="I22">
-        <f t="shared" ref="I22:I32" si="6">D22*E22*G22</f>
+      <c r="I26">
+        <f t="shared" ref="I26:I36" si="6">D26*E26*G26</f>
         <v>0</v>
       </c>
-      <c r="J22">
-        <f t="shared" ref="J22:J32" si="7">H22+I22</f>
+      <c r="J26">
+        <f t="shared" ref="J26:J36" si="7">H26+I26</f>
         <v>240264.99999999997</v>
       </c>
-      <c r="L22">
-        <f>L21+I22</f>
+      <c r="L26">
+        <f>L25+I26</f>
         <v>307260.04547368421</v>
       </c>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B23" s="7">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B27" s="7">
         <v>45833</v>
       </c>
-      <c r="C23">
+      <c r="C27">
         <v>1.6237697368421053</v>
       </c>
-      <c r="D23">
+      <c r="D27">
         <v>1.4613947368421052</v>
       </c>
-      <c r="E23">
+      <c r="E27">
         <v>31.103999999999999</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F27" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G23">
+      <c r="G27">
         <v>7000</v>
       </c>
-      <c r="H23">
+      <c r="H27">
         <f t="shared" si="5"/>
         <v>246813</v>
       </c>
-      <c r="I23">
+      <c r="I27">
         <f t="shared" si="6"/>
         <v>318186.55326315784</v>
       </c>
-      <c r="J23">
+      <c r="J27">
         <f t="shared" si="7"/>
         <v>564999.55326315784</v>
       </c>
-      <c r="L23">
-        <f t="shared" ref="L23:L32" si="8">L22+I23</f>
+      <c r="L27">
+        <f t="shared" ref="L27:L36" si="8">L26+I27</f>
         <v>625446.59873684205</v>
       </c>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B24" s="7">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B28" s="7">
         <v>45863</v>
       </c>
-      <c r="C24">
+      <c r="C28">
         <v>1.6237697368421053</v>
       </c>
-      <c r="D24">
+      <c r="D28">
         <v>0.97426315789473683</v>
       </c>
-      <c r="E24">
+      <c r="E28">
         <v>31.103999999999999</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F28" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G24">
+      <c r="G28">
         <v>7000</v>
       </c>
-      <c r="H24">
+      <c r="H28">
         <f t="shared" si="5"/>
         <v>246813</v>
       </c>
-      <c r="I24">
+      <c r="I28">
         <f t="shared" si="6"/>
         <v>212124.36884210526</v>
       </c>
-      <c r="J24">
+      <c r="J28">
         <f t="shared" si="7"/>
         <v>458937.36884210526</v>
       </c>
-      <c r="L24">
+      <c r="L28">
         <f t="shared" si="8"/>
         <v>837570.96757894731</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="7">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B29" s="7">
         <v>45894</v>
       </c>
-      <c r="C25">
+      <c r="C29">
         <v>1.6237697368421053</v>
       </c>
-      <c r="D25">
+      <c r="D29">
         <v>0.97426315789473683</v>
       </c>
-      <c r="E25">
+      <c r="E29">
         <v>31.103999999999999</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F29" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G25">
+      <c r="G29">
         <v>6657.9218106995604</v>
       </c>
-      <c r="H25">
+      <c r="H29">
         <f t="shared" si="5"/>
         <v>246813</v>
       </c>
-      <c r="I25">
+      <c r="I29">
         <f t="shared" si="6"/>
         <v>201758.20884210442</v>
       </c>
-      <c r="J25">
+      <c r="J29">
         <f t="shared" si="7"/>
         <v>448571.20884210442</v>
       </c>
-      <c r="L25">
+      <c r="L29">
         <f t="shared" si="8"/>
         <v>1039329.1764210517</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B26" s="7">
+    <row r="30" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B30" s="7">
         <v>45925</v>
       </c>
-      <c r="C26">
+      <c r="C30">
         <v>1.6237697368421053</v>
       </c>
-      <c r="D26">
+      <c r="D30">
         <v>0.32475657894736842</v>
       </c>
-      <c r="E26">
+      <c r="E30">
         <v>31.103999999999999</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F30" s="8">
         <v>4886.8312757201647</v>
       </c>
-      <c r="G26">
+      <c r="G30">
         <v>3279.3186831275698</v>
       </c>
-      <c r="H26">
+      <c r="H30">
         <f t="shared" si="5"/>
         <v>246813</v>
       </c>
-      <c r="I26">
+      <c r="I30">
         <f t="shared" si="6"/>
         <v>33125.147774079975</v>
       </c>
-      <c r="J26">
+      <c r="J30">
         <f t="shared" si="7"/>
         <v>279938.14777407999</v>
-      </c>
-      <c r="L26">
-        <f t="shared" si="8"/>
-        <v>1072454.3241951317</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B27" s="7">
-        <v>45955</v>
-      </c>
-      <c r="C27">
-        <v>1.7219534883720931</v>
-      </c>
-      <c r="D27">
-        <v>1.7219534883720931</v>
-      </c>
-      <c r="E27">
-        <v>31.103999999999999</v>
-      </c>
-      <c r="F27" s="8">
-        <v>2764.9176954732511</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <f t="shared" si="5"/>
-        <v>148088</v>
-      </c>
-      <c r="I27">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <f t="shared" si="7"/>
-        <v>148088</v>
-      </c>
-      <c r="L27">
-        <f t="shared" si="8"/>
-        <v>1072454.3241951317</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B28" s="7">
-        <v>45986</v>
-      </c>
-      <c r="C28">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="D28">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="E28">
-        <v>31.103999999999999</v>
-      </c>
-      <c r="F28" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <f t="shared" si="5"/>
-        <v>148088.00000000003</v>
-      </c>
-      <c r="I28">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <f t="shared" si="7"/>
-        <v>148088.00000000003</v>
-      </c>
-      <c r="L28">
-        <f t="shared" si="8"/>
-        <v>1072454.3241951317</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B29" s="7">
-        <v>46016</v>
-      </c>
-      <c r="C29">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="D29">
-        <v>2.2939030624099632</v>
-      </c>
-      <c r="E29">
-        <v>31.103999999999999</v>
-      </c>
-      <c r="F29" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <f t="shared" si="5"/>
-        <v>148088.00000000003</v>
-      </c>
-      <c r="I29">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <f t="shared" si="7"/>
-        <v>148088.00000000003</v>
-      </c>
-      <c r="L29">
-        <f t="shared" si="8"/>
-        <v>1072454.3241951317</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B30" s="7">
-        <v>46047</v>
-      </c>
-      <c r="C30">
-        <v>1.720433105627585</v>
-      </c>
-      <c r="D30">
-        <v>0.28673497839118917</v>
-      </c>
-      <c r="E30">
-        <v>31.103999999999999</v>
-      </c>
-      <c r="F30" s="8">
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <f t="shared" si="5"/>
-        <v>148088.00000000003</v>
-      </c>
-      <c r="I30">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <f t="shared" si="7"/>
-        <v>148088.00000000003</v>
       </c>
       <c r="L30">
         <f t="shared" si="8"/>
         <v>1072454.3241951317</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B31" s="7">
-        <v>46078</v>
+        <v>45955</v>
       </c>
       <c r="C31">
-        <v>1.720433105627585</v>
+        <v>1.7219534883720931</v>
       </c>
       <c r="D31">
-        <v>1.4336865095961708</v>
+        <v>1.7219534883720931</v>
       </c>
       <c r="E31">
         <v>31.103999999999999</v>
       </c>
       <c r="F31" s="8">
-        <v>2767.3611111111113</v>
+        <v>2764.9176954732511</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
         <f t="shared" si="5"/>
-        <v>148088.00000000003</v>
+        <v>148088</v>
       </c>
       <c r="I31">
         <f t="shared" si="6"/>
@@ -7182,22 +11533,22 @@
       </c>
       <c r="J31">
         <f t="shared" si="7"/>
-        <v>148088.00000000003</v>
+        <v>148088</v>
       </c>
       <c r="L31">
         <f t="shared" si="8"/>
         <v>1072454.3241951317</v>
       </c>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B32" s="7">
-        <v>46106</v>
+        <v>45986</v>
       </c>
       <c r="C32">
         <v>1.720433105627585</v>
       </c>
       <c r="D32">
-        <v>1.1469515312049816</v>
+        <v>1.720433105627585</v>
       </c>
       <c r="E32">
         <v>31.103999999999999</v>
@@ -7225,560 +11576,1252 @@
         <v>1072454.3241951317</v>
       </c>
     </row>
-    <row r="33" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="F33">
-        <f>SUM(F21:F32)</f>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B33" s="7">
+        <v>46016</v>
+      </c>
+      <c r="C33">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="D33">
+        <v>2.2939030624099632</v>
+      </c>
+      <c r="E33">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="F33" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="5"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="7"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="8"/>
+        <v>1072454.3241951317</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B34" s="7">
+        <v>46047</v>
+      </c>
+      <c r="C34">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="D34">
+        <v>0.28673497839118917</v>
+      </c>
+      <c r="E34">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="F34" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="5"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="7"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="8"/>
+        <v>1072454.3241951317</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B35" s="7">
+        <v>46078</v>
+      </c>
+      <c r="C35">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="D35">
+        <v>1.4336865095961708</v>
+      </c>
+      <c r="E35">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="F35" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="5"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="7"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="8"/>
+        <v>1072454.3241951317</v>
+      </c>
+    </row>
+    <row r="36" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="B36" s="7">
+        <v>46106</v>
+      </c>
+      <c r="C36">
+        <v>1.720433105627585</v>
+      </c>
+      <c r="D36">
+        <v>1.1469515312049816</v>
+      </c>
+      <c r="E36">
+        <v>31.103999999999999</v>
+      </c>
+      <c r="F36" s="8">
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="5"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="7"/>
+        <v>148088.00000000003</v>
+      </c>
+      <c r="L36">
+        <f t="shared" si="8"/>
+        <v>1072454.3241951317</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="F37">
+        <f>SUM(F25:F36)</f>
         <v>45922.710905349784</v>
       </c>
-      <c r="G33">
-        <f>SUM(G21:G32)</f>
+      <c r="G37">
+        <f>SUM(G25:G36)</f>
         <v>37937.240493827128</v>
       </c>
-      <c r="I33" s="9">
-        <f>SUM(I21:I32)</f>
+      <c r="H37" s="9">
+        <f>SUM(H25:H36)</f>
+        <v>2348425</v>
+      </c>
+      <c r="I37" s="9">
+        <f>SUM(I25:I36)</f>
         <v>1072454.3241951317</v>
       </c>
-      <c r="J33" s="9">
-        <f>SUM(J21:J32)</f>
+      <c r="J37" s="9">
+        <f>SUM(J25:J36)</f>
         <v>3420879.3241951317</v>
       </c>
     </row>
-    <row r="34" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="I34">
-        <f>I33/G33</f>
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="I38">
+        <f>I37/G37</f>
         <v>28.269170615338606</v>
       </c>
     </row>
-    <row r="37" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="F37" t="s">
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="F41" t="s">
         <v>39</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G41" t="s">
         <v>40</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H41" t="s">
         <v>41</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I41" t="s">
         <v>43</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J41" t="s">
         <v>42</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K41" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="38" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E38" s="7">
+      <c r="N41" t="s">
+        <v>49</v>
+      </c>
+      <c r="O41" t="s">
+        <v>51</v>
+      </c>
+      <c r="P41" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>50</v>
+      </c>
+      <c r="R41" t="s">
+        <v>54</v>
+      </c>
+      <c r="S41" t="s">
+        <v>52</v>
+      </c>
+      <c r="T41" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E42" s="7">
         <v>45772</v>
       </c>
-      <c r="F38">
-        <f>SUM(F5:G5)</f>
+      <c r="F42">
+        <f>SUM(F9:G9)</f>
         <v>9773.6625514403295</v>
       </c>
-      <c r="G38">
-        <f>SUM(F21:G21)</f>
+      <c r="G42">
+        <f>SUM(F25:G25)</f>
         <v>11886.831275720164</v>
       </c>
-      <c r="H38">
-        <f>G38-F38</f>
+      <c r="H42">
+        <f>G42-F42</f>
         <v>2113.1687242798344</v>
       </c>
-      <c r="I38">
+      <c r="I42">
         <v>0.05</v>
       </c>
-      <c r="J38">
-        <f t="shared" ref="J38:J49" si="9">H38*I38*K38</f>
+      <c r="J42">
+        <f t="shared" ref="J42:J53" si="9">H42*I42*K42</f>
         <v>2641.4609053497929</v>
       </c>
-      <c r="K38">
+      <c r="K42">
         <v>25</v>
       </c>
-    </row>
-    <row r="39" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E39" s="7">
+      <c r="N42">
+        <v>446884</v>
+      </c>
+      <c r="O42">
+        <f>SUM(P42:Q42)</f>
+        <v>542281.50637903402</v>
+      </c>
+      <c r="P42">
+        <v>2641.4609053497929</v>
+      </c>
+      <c r="Q42">
+        <v>539640.04547368421</v>
+      </c>
+      <c r="R42" s="7">
+        <v>45772</v>
+      </c>
+      <c r="S42">
+        <f>N42</f>
+        <v>446884</v>
+      </c>
+      <c r="T42">
+        <f>O42</f>
+        <v>542281.50637903402</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E43" s="7">
         <v>45802</v>
       </c>
-      <c r="F39">
-        <f t="shared" ref="F39:F49" si="10">SUM(F6:G6)</f>
+      <c r="F43">
+        <f t="shared" ref="F43:F53" si="10">SUM(F10:G10)</f>
         <v>5079.7325102880659</v>
       </c>
-      <c r="G39">
-        <f t="shared" ref="G39:G49" si="11">SUM(F22:G22)</f>
+      <c r="G43">
+        <f t="shared" ref="G43:G53" si="11">SUM(F26:G26)</f>
         <v>11886.831275720164</v>
       </c>
-      <c r="H39">
-        <f>H38+G39-F39</f>
+      <c r="H43">
+        <f>H42+G43-F43</f>
         <v>8920.2674897119323</v>
       </c>
-      <c r="I39">
+      <c r="I43">
         <v>0.05</v>
       </c>
-      <c r="J39">
+      <c r="J43">
         <f t="shared" si="9"/>
         <v>11150.334362139914</v>
       </c>
-      <c r="K39">
+      <c r="K43">
         <v>25</v>
       </c>
-    </row>
-    <row r="40" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E40" s="7">
+      <c r="N43">
+        <v>240264.99999999997</v>
+      </c>
+      <c r="O43">
+        <f t="shared" ref="O43:O53" si="12">SUM(P43:Q43)</f>
+        <v>251415.3343621399</v>
+      </c>
+      <c r="P43">
+        <v>11150.334362139914</v>
+      </c>
+      <c r="Q43">
+        <v>240264.99999999997</v>
+      </c>
+      <c r="R43" s="7">
+        <v>45802</v>
+      </c>
+      <c r="S43">
+        <f>N43+S42</f>
+        <v>687149</v>
+      </c>
+      <c r="T43">
+        <f>O43+T42</f>
+        <v>793696.84074117395</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E44" s="7">
         <v>45833</v>
       </c>
-      <c r="F40">
+      <c r="F44">
         <f t="shared" si="10"/>
         <v>9902.2633744855975</v>
       </c>
-      <c r="G40">
+      <c r="G44">
         <f t="shared" si="11"/>
         <v>11886.831275720164</v>
       </c>
-      <c r="H40">
-        <f t="shared" ref="H40:H49" si="12">H39+G40-F40</f>
+      <c r="H44">
+        <f t="shared" ref="H44:H53" si="13">H43+G44-F44</f>
         <v>10904.835390946499</v>
       </c>
-      <c r="I40">
+      <c r="I44">
         <v>0.05</v>
       </c>
-      <c r="J40">
+      <c r="J44">
         <f t="shared" si="9"/>
         <v>13631.044238683122</v>
       </c>
-      <c r="K40">
+      <c r="K44">
         <v>25</v>
       </c>
-    </row>
-    <row r="41" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E41" s="7">
+      <c r="N44">
+        <v>474790.57894736843</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="12"/>
+        <v>578630.59750184091</v>
+      </c>
+      <c r="P44">
+        <v>13631.044238683122</v>
+      </c>
+      <c r="Q44">
+        <v>564999.55326315784</v>
+      </c>
+      <c r="R44" s="7">
+        <v>45833</v>
+      </c>
+      <c r="S44">
+        <f t="shared" ref="S44:T53" si="14">N44+S43</f>
+        <v>1161939.5789473685</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="14"/>
+        <v>1372327.4382430147</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E45" s="7">
         <v>45863</v>
       </c>
-      <c r="F41">
+      <c r="F45">
         <f t="shared" si="10"/>
         <v>8326.9032921810704</v>
       </c>
-      <c r="G41">
+      <c r="G45">
         <f t="shared" si="11"/>
         <v>11886.831275720164</v>
       </c>
-      <c r="H41">
-        <f t="shared" si="12"/>
+      <c r="H45">
+        <f t="shared" si="13"/>
         <v>14464.763374485594</v>
       </c>
-      <c r="I41">
+      <c r="I45">
         <v>0.05</v>
       </c>
-      <c r="J41">
+      <c r="J45">
         <f t="shared" si="9"/>
         <v>18080.954218106992</v>
       </c>
-      <c r="K41">
+      <c r="K45">
         <v>25</v>
       </c>
-    </row>
-    <row r="42" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E42" s="7">
+      <c r="N45">
+        <v>351059.15789473685</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="12"/>
+        <v>477018.32306021225</v>
+      </c>
+      <c r="P45">
+        <v>18080.954218106992</v>
+      </c>
+      <c r="Q45">
+        <v>458937.36884210526</v>
+      </c>
+      <c r="R45" s="7">
+        <v>45863</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="14"/>
+        <v>1512998.7368421054</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="14"/>
+        <v>1849345.7613032269</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E46" s="7">
         <v>45894</v>
       </c>
-      <c r="F42">
+      <c r="F46">
         <f t="shared" si="10"/>
         <v>8326.9032921810704</v>
       </c>
-      <c r="G42">
+      <c r="G46">
         <f t="shared" si="11"/>
         <v>11544.753086419725</v>
       </c>
-      <c r="H42">
-        <f t="shared" si="12"/>
+      <c r="H46">
+        <f t="shared" si="13"/>
         <v>17682.613168724245</v>
       </c>
-      <c r="I42">
+      <c r="I46">
         <v>0.05</v>
       </c>
-      <c r="J42">
+      <c r="J46">
         <f t="shared" si="9"/>
         <v>22103.26646090531</v>
       </c>
-      <c r="K42">
+      <c r="K46">
         <v>25</v>
       </c>
-    </row>
-    <row r="43" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E43" s="7">
+      <c r="N46">
+        <v>351059.15789473685</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="12"/>
+        <v>470674.47530300973</v>
+      </c>
+      <c r="P46">
+        <v>22103.26646090531</v>
+      </c>
+      <c r="Q46">
+        <v>448571.20884210442</v>
+      </c>
+      <c r="R46" s="7">
+        <v>45894</v>
+      </c>
+      <c r="S46">
+        <f t="shared" si="14"/>
+        <v>1864057.8947368423</v>
+      </c>
+      <c r="T46">
+        <f t="shared" si="14"/>
+        <v>2320020.2366062365</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E47" s="7">
         <v>45925</v>
       </c>
-      <c r="F43">
+      <c r="F47">
         <f t="shared" si="10"/>
         <v>6237.1399176954737</v>
       </c>
-      <c r="G43">
+      <c r="G47">
         <f t="shared" si="11"/>
         <v>8166.1499588477345</v>
       </c>
-      <c r="H43">
-        <f t="shared" si="12"/>
+      <c r="H47">
+        <f t="shared" si="13"/>
         <v>19611.623209876507</v>
       </c>
-      <c r="I43">
+      <c r="I47">
         <v>0.05</v>
       </c>
-      <c r="J43">
+      <c r="J47">
         <f t="shared" si="9"/>
         <v>24514.529012345633</v>
       </c>
-      <c r="K43">
+      <c r="K47">
         <v>25</v>
       </c>
-    </row>
-    <row r="44" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E44" s="7">
+      <c r="N47">
+        <v>260452.77631578947</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="12"/>
+        <v>304452.67678642564</v>
+      </c>
+      <c r="P47">
+        <v>24514.529012345633</v>
+      </c>
+      <c r="Q47">
+        <v>279938.14777407999</v>
+      </c>
+      <c r="R47" s="7">
+        <v>45925</v>
+      </c>
+      <c r="S47">
+        <f t="shared" si="14"/>
+        <v>2124510.6710526319</v>
+      </c>
+      <c r="T47">
+        <f t="shared" si="14"/>
+        <v>2624472.9133926621</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="E48" s="7">
         <v>45955</v>
       </c>
-      <c r="F44">
+      <c r="F48">
         <f t="shared" si="10"/>
         <v>5208.333333333333</v>
       </c>
-      <c r="G44">
+      <c r="G48">
         <f t="shared" si="11"/>
         <v>2764.9176954732511</v>
       </c>
-      <c r="H44">
-        <f t="shared" si="12"/>
+      <c r="H48">
+        <f t="shared" si="13"/>
         <v>17168.207572016425</v>
       </c>
-      <c r="I44">
+      <c r="I48">
         <v>0.05</v>
       </c>
-      <c r="J44">
+      <c r="J48">
         <f t="shared" si="9"/>
         <v>21460.259465020532</v>
       </c>
-      <c r="K44">
+      <c r="K48">
         <v>25</v>
       </c>
-    </row>
-    <row r="45" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E45" s="7">
+      <c r="N48">
+        <v>278956.46511627908</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="12"/>
+        <v>169548.25946502053</v>
+      </c>
+      <c r="P48">
+        <v>21460.259465020532</v>
+      </c>
+      <c r="Q48">
+        <v>148088</v>
+      </c>
+      <c r="R48" s="7">
+        <v>45955</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="14"/>
+        <v>2403467.1361689111</v>
+      </c>
+      <c r="T48">
+        <f t="shared" si="14"/>
+        <v>2794021.1728576827</v>
+      </c>
+    </row>
+    <row r="49" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E49" s="7">
         <v>45986</v>
       </c>
-      <c r="F45">
+      <c r="F49">
         <f t="shared" si="10"/>
         <v>6237.1399176954737</v>
-      </c>
-      <c r="G45">
-        <f t="shared" si="11"/>
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H45">
-        <f t="shared" si="12"/>
-        <v>13698.428765432065</v>
-      </c>
-      <c r="I45">
-        <v>0.05</v>
-      </c>
-      <c r="J45">
-        <f t="shared" si="9"/>
-        <v>17123.035956790081</v>
-      </c>
-      <c r="K45">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E46" s="7">
-        <v>46016</v>
-      </c>
-      <c r="F46">
-        <f t="shared" si="10"/>
-        <v>7298.0967078189306</v>
-      </c>
-      <c r="G46">
-        <f t="shared" si="11"/>
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H46">
-        <f t="shared" si="12"/>
-        <v>9167.6931687242432</v>
-      </c>
-      <c r="I46">
-        <v>0.05</v>
-      </c>
-      <c r="J46">
-        <f t="shared" si="9"/>
-        <v>11459.616460905305</v>
-      </c>
-      <c r="K46">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E47" s="7">
-        <v>46047</v>
-      </c>
-      <c r="F47">
-        <f t="shared" si="10"/>
-        <v>3632.9732510288068</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="11"/>
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H47">
-        <f t="shared" si="12"/>
-        <v>8302.0810288065477</v>
-      </c>
-      <c r="I47">
-        <v>0.05</v>
-      </c>
-      <c r="J47">
-        <f t="shared" si="9"/>
-        <v>10377.601286008185</v>
-      </c>
-      <c r="K47">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E48" s="7">
-        <v>46078</v>
-      </c>
-      <c r="F48">
-        <f t="shared" si="10"/>
-        <v>5722.7366255144034</v>
-      </c>
-      <c r="G48">
-        <f t="shared" si="11"/>
-        <v>2767.3611111111113</v>
-      </c>
-      <c r="H48">
-        <f t="shared" si="12"/>
-        <v>5346.7055144032556</v>
-      </c>
-      <c r="I48">
-        <v>0.05</v>
-      </c>
-      <c r="J48">
-        <f t="shared" si="9"/>
-        <v>6683.3818930040688</v>
-      </c>
-      <c r="K48">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E49" s="7">
-        <v>46106</v>
-      </c>
-      <c r="F49">
-        <f t="shared" si="10"/>
-        <v>5208.333333333333</v>
       </c>
       <c r="G49">
         <f t="shared" si="11"/>
         <v>2767.3611111111113</v>
       </c>
       <c r="H49">
-        <f t="shared" si="12"/>
-        <v>2905.7332921810339</v>
+        <f t="shared" si="13"/>
+        <v>13698.428765432065</v>
       </c>
       <c r="I49">
         <v>0.05</v>
       </c>
       <c r="J49">
         <f t="shared" si="9"/>
-        <v>3632.1666152262928</v>
+        <v>17123.035956790081</v>
       </c>
       <c r="K49">
         <v>25</v>
       </c>
-    </row>
-    <row r="50" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="I50" t="s">
+      <c r="N49">
+        <v>333764.02249175153</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="12"/>
+        <v>165211.03595679012</v>
+      </c>
+      <c r="P49">
+        <v>17123.035956790081</v>
+      </c>
+      <c r="Q49">
+        <v>148088.00000000003</v>
+      </c>
+      <c r="R49" s="7">
+        <v>45986</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="14"/>
+        <v>2737231.1586606628</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="14"/>
+        <v>2959232.2088144729</v>
+      </c>
+    </row>
+    <row r="50" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E50" s="7">
+        <v>46016</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="10"/>
+        <v>7298.0967078189306</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="11"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="13"/>
+        <v>9167.6931687242432</v>
+      </c>
+      <c r="I50">
+        <v>0.05</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="9"/>
+        <v>11459.616460905305</v>
+      </c>
+      <c r="K50">
+        <v>25</v>
+      </c>
+      <c r="N50">
+        <v>471353.99516706169</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="12"/>
+        <v>159547.61646090532</v>
+      </c>
+      <c r="P50">
+        <v>11459.616460905305</v>
+      </c>
+      <c r="Q50">
+        <v>148088.00000000003</v>
+      </c>
+      <c r="R50" s="7">
+        <v>46016</v>
+      </c>
+      <c r="S50">
+        <f t="shared" si="14"/>
+        <v>3208585.1538277245</v>
+      </c>
+      <c r="T50">
+        <f t="shared" si="14"/>
+        <v>3118779.8252753783</v>
+      </c>
+    </row>
+    <row r="51" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E51" s="7">
+        <v>46047</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="10"/>
+        <v>3632.9732510288068</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="11"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="13"/>
+        <v>8302.0810288065477</v>
+      </c>
+      <c r="I51">
+        <v>0.05</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="9"/>
+        <v>10377.601286008185</v>
+      </c>
+      <c r="K51">
+        <v>25</v>
+      </c>
+      <c r="N51">
+        <v>155808.05255820439</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="12"/>
+        <v>158465.60128600823</v>
+      </c>
+      <c r="P51">
+        <v>10377.601286008185</v>
+      </c>
+      <c r="Q51">
+        <v>148088.00000000003</v>
+      </c>
+      <c r="R51" s="7">
+        <v>46047</v>
+      </c>
+      <c r="S51">
+        <f t="shared" si="14"/>
+        <v>3364393.2063859291</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="14"/>
+        <v>3277245.4265613863</v>
+      </c>
+    </row>
+    <row r="52" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E52" s="7">
+        <v>46078</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="10"/>
+        <v>5722.7366255144034</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="11"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="13"/>
+        <v>5346.7055144032556</v>
+      </c>
+      <c r="I52">
+        <v>0.05</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="9"/>
+        <v>6683.3818930040688</v>
+      </c>
+      <c r="K52">
+        <v>25</v>
+      </c>
+      <c r="N52">
+        <v>279878.19870811841</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="12"/>
+        <v>154771.38189300409</v>
+      </c>
+      <c r="P52">
+        <v>6683.3818930040688</v>
+      </c>
+      <c r="Q52">
+        <v>148088.00000000003</v>
+      </c>
+      <c r="R52" s="7">
+        <v>46078</v>
+      </c>
+      <c r="S52">
+        <f t="shared" si="14"/>
+        <v>3644271.4050940475</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="14"/>
+        <v>3432016.8084543906</v>
+      </c>
+    </row>
+    <row r="53" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="E53" s="7">
+        <v>46106</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="10"/>
+        <v>5208.333333333333</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="11"/>
+        <v>2767.3611111111113</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="13"/>
+        <v>2905.7332921810339</v>
+      </c>
+      <c r="I53">
+        <v>0.05</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="9"/>
+        <v>3632.1666152262928</v>
+      </c>
+      <c r="K53">
+        <v>25</v>
+      </c>
+      <c r="N53">
+        <v>235169.14805520704</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="12"/>
+        <v>151720.16661522634</v>
+      </c>
+      <c r="P53">
+        <v>3632.1666152262928</v>
+      </c>
+      <c r="Q53">
+        <v>148088.00000000003</v>
+      </c>
+      <c r="R53" s="7">
+        <v>46106</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="14"/>
+        <v>3879440.5531492545</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="14"/>
+        <v>3583736.9750696169</v>
+      </c>
+    </row>
+    <row r="54" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="I54" t="s">
         <v>42</v>
       </c>
-      <c r="J50" s="9">
-        <f>SUM(J38:J49)</f>
+      <c r="J54" s="9">
+        <f>SUM(J42:J53)</f>
         <v>162857.65087448523</v>
       </c>
     </row>
-    <row r="52" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="I52" t="s">
+    <row r="56" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="I56" t="s">
         <v>44</v>
       </c>
-      <c r="J52">
-        <f>SUM(J33+J50)</f>
+      <c r="J56">
+        <f>SUM(J37+J54)</f>
         <v>3583736.9750696169</v>
       </c>
     </row>
-    <row r="54" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="I54" t="s">
+    <row r="58" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="I58" t="s">
         <v>46</v>
       </c>
-      <c r="J54">
-        <f>(J17-J52)/J17</f>
+      <c r="J58">
+        <f>(J21-J56)/J21</f>
         <v>7.622325281917032E-2</v>
       </c>
     </row>
-    <row r="59" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="G59" t="s">
+    <row r="59" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="L59" s="8"/>
+      <c r="M59" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O59" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="L60" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M60" s="8">
+        <v>1531015.5531492536</v>
+      </c>
+      <c r="N60" s="8">
+        <v>1072454.3241951317</v>
+      </c>
+      <c r="O60" s="8">
+        <f>100*(M60-N60)/M60</f>
+        <v>29.95144157816523</v>
+      </c>
+    </row>
+    <row r="61" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="L61" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="M61" s="8">
+        <v>2348425</v>
+      </c>
+      <c r="N61" s="8">
+        <v>2348425</v>
+      </c>
+      <c r="O61" s="8">
+        <f t="shared" ref="O61:O63" si="15">100*(M61-N61)/M61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="L62" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M62" s="8">
+        <v>0</v>
+      </c>
+      <c r="N62" s="11">
+        <v>162857.65087448523</v>
+      </c>
+      <c r="O62" s="8"/>
+    </row>
+    <row r="63" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="G63" t="s">
         <v>47</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H63" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="60" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="F60" s="7">
+      <c r="J63" t="s">
+        <v>56</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M63" s="8">
+        <f>SUM(M60:M62)</f>
+        <v>3879440.5531492536</v>
+      </c>
+      <c r="N63" s="8">
+        <f>SUM(N60:N62)</f>
+        <v>3583736.9750696169</v>
+      </c>
+      <c r="O63" s="8">
+        <f t="shared" si="15"/>
+        <v>7.6223252819170106</v>
+      </c>
+    </row>
+    <row r="64" spans="5:20" x14ac:dyDescent="0.2">
+      <c r="F64" s="7">
         <v>45833</v>
       </c>
-      <c r="G60" s="10">
+      <c r="G64" s="10">
         <v>185342.5</v>
       </c>
-      <c r="H60">
+      <c r="H64">
         <v>9902.2633744855975</v>
       </c>
-      <c r="I60">
-        <f>H60/G60</f>
+      <c r="I64">
+        <f t="shared" ref="I64:I73" si="16">H64/G64</f>
         <v>5.3426836124934096E-2</v>
       </c>
-    </row>
-    <row r="61" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="F61" s="7">
+      <c r="J64">
+        <v>1000</v>
+      </c>
+      <c r="K64">
+        <f>I64*J64</f>
+        <v>53.426836124934098</v>
+      </c>
+    </row>
+    <row r="65" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F65" s="7">
         <v>45863</v>
       </c>
-      <c r="G61" s="10">
+      <c r="G65" s="10">
         <v>211816.5</v>
       </c>
-      <c r="H61">
+      <c r="H65">
         <v>8326.9032921810704</v>
       </c>
-      <c r="I61">
-        <f t="shared" ref="I61:I69" si="13">H61/G61</f>
+      <c r="I65">
+        <f t="shared" si="16"/>
         <v>3.9311872739758565E-2</v>
       </c>
-    </row>
-    <row r="62" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="F62" s="7">
+      <c r="J65">
+        <v>1000</v>
+      </c>
+      <c r="K65">
+        <f t="shared" ref="K65:K73" si="17">I65*J65</f>
+        <v>39.311872739758563</v>
+      </c>
+    </row>
+    <row r="66" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F66" s="7">
         <v>45894</v>
       </c>
-      <c r="G62" s="10">
+      <c r="G66" s="10">
         <v>208414.5</v>
       </c>
-      <c r="H62">
+      <c r="H66">
         <v>8326.9032921810704</v>
       </c>
-      <c r="I62">
-        <f t="shared" si="13"/>
+      <c r="I66">
+        <f t="shared" si="16"/>
         <v>3.9953569891639354E-2</v>
       </c>
-    </row>
-    <row r="63" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="F63" s="7">
+      <c r="J66">
+        <v>1000</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="17"/>
+        <v>39.953569891639354</v>
+      </c>
+    </row>
+    <row r="67" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F67" s="7">
         <v>45925</v>
       </c>
-      <c r="G63" s="10">
+      <c r="G67" s="10">
         <v>204928.5</v>
       </c>
-      <c r="H63">
+      <c r="H67">
         <v>6237.1399176954737</v>
       </c>
-      <c r="I63">
-        <f t="shared" si="13"/>
+      <c r="I67">
+        <f t="shared" si="16"/>
         <v>3.0435688143403548E-2</v>
       </c>
-    </row>
-    <row r="64" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="F64" s="7">
+      <c r="J67">
+        <v>1000</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="17"/>
+        <v>30.435688143403549</v>
+      </c>
+    </row>
+    <row r="68" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F68" s="7">
         <v>45955</v>
       </c>
-      <c r="G64" s="10">
+      <c r="G68" s="10">
         <v>201565</v>
       </c>
-      <c r="H64">
+      <c r="H68">
         <v>5208.333333333333</v>
       </c>
-      <c r="I64">
-        <f t="shared" si="13"/>
+      <c r="I68">
+        <f t="shared" si="16"/>
         <v>2.5839472792068729E-2</v>
       </c>
-    </row>
-    <row r="65" spans="6:9" x14ac:dyDescent="0.2">
-      <c r="F65" s="7">
+      <c r="J68">
+        <v>1000</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="17"/>
+        <v>25.839472792068729</v>
+      </c>
+    </row>
+    <row r="69" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F69" s="7">
         <v>45986</v>
       </c>
-      <c r="G65" s="10">
+      <c r="G69" s="10">
         <v>198121</v>
       </c>
-      <c r="H65">
+      <c r="H69">
         <v>6237.1399176954737</v>
       </c>
-      <c r="I65">
-        <f t="shared" si="13"/>
+      <c r="I69">
+        <f t="shared" si="16"/>
         <v>3.1481467980150883E-2</v>
       </c>
-    </row>
-    <row r="66" spans="6:9" x14ac:dyDescent="0.2">
-      <c r="F66" s="7">
+      <c r="J69">
+        <v>1000</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="17"/>
+        <v>31.481467980150882</v>
+      </c>
+    </row>
+    <row r="70" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F70" s="7">
         <v>46016</v>
       </c>
-      <c r="G66" s="10">
+      <c r="G70" s="10">
         <v>155050</v>
       </c>
-      <c r="H66">
+      <c r="H70">
         <v>7298.0967078189306</v>
       </c>
-      <c r="I66">
-        <f t="shared" si="13"/>
+      <c r="I70">
+        <f t="shared" si="16"/>
         <v>4.7069311240367173E-2</v>
       </c>
-    </row>
-    <row r="67" spans="6:9" x14ac:dyDescent="0.2">
-      <c r="F67" s="7">
+      <c r="J70">
+        <v>1000</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="17"/>
+        <v>47.069311240367171</v>
+      </c>
+    </row>
+    <row r="71" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F71" s="7">
         <v>46047</v>
       </c>
-      <c r="G67" s="10">
+      <c r="G71" s="10">
         <v>154700</v>
       </c>
-      <c r="H67">
+      <c r="H71">
         <v>3632.9732510288068</v>
       </c>
-      <c r="I67">
-        <f t="shared" si="13"/>
+      <c r="I71">
+        <f t="shared" si="16"/>
         <v>2.3483989987257963E-2</v>
       </c>
-    </row>
-    <row r="68" spans="6:9" x14ac:dyDescent="0.2">
-      <c r="F68" s="7">
+      <c r="J71">
+        <v>1000</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="17"/>
+        <v>23.483989987257964</v>
+      </c>
+    </row>
+    <row r="72" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F72" s="7">
         <v>46078</v>
       </c>
-      <c r="G68" s="10">
+      <c r="G72" s="10">
         <v>133350</v>
       </c>
-      <c r="H68">
+      <c r="H72">
         <v>5722.7366255144034</v>
       </c>
-      <c r="I68">
-        <f t="shared" si="13"/>
+      <c r="I72">
+        <f t="shared" si="16"/>
         <v>4.2915160296320982E-2</v>
       </c>
-    </row>
-    <row r="69" spans="6:9" x14ac:dyDescent="0.2">
-      <c r="F69" s="7">
+      <c r="J72">
+        <v>1000</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="17"/>
+        <v>42.915160296320984</v>
+      </c>
+    </row>
+    <row r="73" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F73" s="7">
         <v>46106</v>
       </c>
-      <c r="G69" s="10">
+      <c r="G73" s="10">
         <v>132650</v>
       </c>
-      <c r="H69">
+      <c r="H73">
         <v>5208.333333333333</v>
       </c>
-      <c r="I69">
-        <f t="shared" si="13"/>
+      <c r="I73">
+        <f t="shared" si="16"/>
         <v>3.9263726598818945E-2</v>
       </c>
+      <c r="J73">
+        <v>1000</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="17"/>
+        <v>39.263726598818941</v>
+      </c>
+    </row>
+    <row r="76" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F76" s="7">
+        <v>45833</v>
+      </c>
+      <c r="G76">
+        <f>K64</f>
+        <v>53.426836124934098</v>
+      </c>
+    </row>
+    <row r="77" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F77" s="7">
+        <v>45863</v>
+      </c>
+      <c r="G77">
+        <f t="shared" ref="G77:G85" si="18">K65</f>
+        <v>39.311872739758563</v>
+      </c>
+    </row>
+    <row r="78" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F78" s="7">
+        <v>45894</v>
+      </c>
+      <c r="G78">
+        <f t="shared" si="18"/>
+        <v>39.953569891639354</v>
+      </c>
+    </row>
+    <row r="79" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F79" s="7">
+        <v>45925</v>
+      </c>
+      <c r="G79">
+        <f t="shared" si="18"/>
+        <v>30.435688143403549</v>
+      </c>
+    </row>
+    <row r="80" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F80" s="7">
+        <v>45955</v>
+      </c>
+      <c r="G80">
+        <f t="shared" si="18"/>
+        <v>25.839472792068729</v>
+      </c>
+    </row>
+    <row r="81" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F81" s="7">
+        <v>45986</v>
+      </c>
+      <c r="G81">
+        <f t="shared" si="18"/>
+        <v>31.481467980150882</v>
+      </c>
+    </row>
+    <row r="82" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F82" s="7">
+        <v>46016</v>
+      </c>
+      <c r="G82">
+        <f t="shared" si="18"/>
+        <v>47.069311240367171</v>
+      </c>
+    </row>
+    <row r="83" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F83" s="7">
+        <v>46047</v>
+      </c>
+      <c r="G83">
+        <f t="shared" si="18"/>
+        <v>23.483989987257964</v>
+      </c>
+    </row>
+    <row r="84" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F84" s="7">
+        <v>46078</v>
+      </c>
+      <c r="G84">
+        <f t="shared" si="18"/>
+        <v>42.915160296320984</v>
+      </c>
+    </row>
+    <row r="85" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F85" s="7">
+        <v>46106</v>
+      </c>
+      <c r="G85">
+        <f t="shared" si="18"/>
+        <v>39.263726598818941</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H2:H3"/>
+  </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
